--- a/src/main/resources/python/MultifacetedModeling/Results/OnTrain/DKNCOR/SVR.xlsx
+++ b/src/main/resources/python/MultifacetedModeling/Results/OnTrain/DKNCOR/SVR.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="result0" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="result0" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H101"/>
+  <dimension ref="A1:G101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,58 +466,48 @@
           <t>Time</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>d_class</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>[1, 3, 4, 5, 7, 9, 10, 12, 15, 16, 17, 19, 24, 27, 28, 30, 31, 32, 33, 35, 36, 37, 39]</t>
+          <t>[0, 1, 3, 5, 12, 16, 18, 19, 20, 23, 24, 25, 26, 29, 32, 33, 36, 37, 40]</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.807936507936508</t>
+          <t>0.44780219780219777</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.06481957443267088</t>
+          <t>0.06469682132261213</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.05818517387255178</t>
+          <t>0.07045290535911353</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>0.949854483244128</t>
+          <t>0.9321498820420606</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>1.2762339115142822</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>4.56228232383728</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>[1, 8, 9, 12, 19, 21, 22, 25, 29, 30, 32, 33, 34, 35, 36, 37, 39, 41]</t>
+          <t>[0, 4, 6, 9, 12, 14, 21, 22, 23, 25, 32, 33, 35, 37, 38, 39, 42, 43]</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -527,123 +517,108 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.7871031746031746</t>
+          <t>0.5620879120879121</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.06566957252127649</t>
+          <t>0.06495889214034367</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.0572403774991056</t>
+          <t>0.08673676832800381</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>0.9514697624922612</t>
+          <t>0.8971606634390141</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>1.2758843898773193</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>4.645878791809082</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>[3, 4, 10, 11, 12, 13, 16, 19, 23, 26, 27, 29, 31, 32, 35, 42, 43, 44]</t>
+          <t>[0, 1, 4, 5, 8, 9, 12, 14, 18, 23, 24, 25, 29, 32, 33, 34, 35, 40, 41, 42, 44]</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.40793650793650793</t>
+          <t>0.3879120879120879</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.06539205550118704</t>
+          <t>0.06487475649042325</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.05551547518941552</t>
+          <t>0.08886366834280708</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>0.9543505487425545</t>
+          <t>0.8920553141757152</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>1.2750792503356934</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>3</t>
+          <t>4.895490646362305</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>[3, 5, 7, 8, 12, 15, 17, 19, 21, 22, 25, 26, 28, 29, 31, 32, 33, 34, 35, 39, 40, 43, 44]</t>
+          <t>[0, 1, 5, 6, 10, 11, 13, 15, 16, 17, 18, 19, 21, 23, 25, 26, 33, 35, 36, 37, 39, 41, 42, 43]</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.8535714285714285</t>
+          <t>0.9252747252747252</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.06256608023644489</t>
+          <t>0.06534867142029348</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.04889869087184474</t>
+          <t>0.0844209319695756</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>0.9645838047932942</t>
+          <t>0.9025788892758017</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>1.267974853515625</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0</t>
+          <t>4.95621919631958</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>[0, 2, 7, 8, 13, 14, 15, 19, 20, 23, 25, 26, 28, 29, 31, 33, 36, 38, 39, 40, 42, 44]</t>
+          <t>[0, 1, 3, 4, 8, 10, 13, 14, 16, 19, 24, 25, 26, 28, 29, 31, 32, 33, 36, 37, 42, 44]</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -653,921 +628,811 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.8583333333333334</t>
+          <t>0.8565934065934067</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.06303262770310955</t>
+          <t>0.0675325541364006</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.05534998276242807</t>
+          <t>0.07050289352881742</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>0.9546223064177154</t>
+          <t>0.9320535650358432</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>1.2826659679412842</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>0</t>
+          <t>4.990712881088257</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>[1, 4, 5, 13, 14, 15, 16, 17, 19, 20, 21, 25, 28, 29, 30, 32, 33, 34, 36, 40]</t>
+          <t>[0, 1, 3, 6, 7, 8, 11, 13, 14, 16, 17, 18, 20, 21, 25, 26, 30, 32, 33, 34, 35, 37, 39, 42, 44]</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.5416666666666667</t>
+          <t>0.8906593406593406</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.06414533864893121</t>
+          <t>0.06685273494125976</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.05735973688244762</t>
+          <t>0.0803126213707516</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>0.9512671580069115</t>
+          <t>0.9118300905232327</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>1.2852160930633545</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>4.763794422149658</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>[1, 5, 6, 7, 11, 13, 14, 15, 17, 19, 20, 25, 27, 28, 29, 31, 32, 33, 35, 36, 40, 41, 42, 43, 44]</t>
+          <t>[2, 3, 5, 7, 8, 11, 18, 19, 22, 23, 24, 25, 29, 30, 33, 34, 35, 36, 38]</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1.1126984126984127</t>
+          <t>0.4906593406593407</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>0.06618208943712883</t>
+          <t>0.06710868375818144</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0.050255246881276264</t>
+          <t>0.07961594738763866</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>0.9625915029622693</t>
+          <t>0.9133531204435826</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>1.268850326538086</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>3</t>
+          <t>4.791616201400757</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>[4, 5, 7, 10, 12, 16, 17, 18, 21, 22, 25, 29, 31, 37, 42, 43]</t>
+          <t>[3, 6, 7, 11, 13, 19, 21, 23, 24, 25, 30, 35, 36, 37, 38, 39, 42, 44]</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.3732142857142857</t>
+          <t>0.289010989010989</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.06096209220248635</t>
+          <t>0.06425288076336455</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.03512768750566675</t>
+          <t>0.07786411203632418</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0.9817229306572706</t>
+          <t>0.9171242516972171</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1.2882721424102783</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>0</t>
+          <t>4.8348917961120605</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>[1, 2, 4, 7, 14, 15, 17, 21, 22, 25, 26, 28, 32, 34, 35, 41, 44]</t>
+          <t>[0, 1, 2, 3, 4, 6, 8, 9, 10, 11, 12, 16, 20, 24, 25, 32, 33, 34, 35, 38, 42, 44]</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.4996031746031746</t>
+          <t>0.8494505494505495</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0.06328147888744194</t>
+          <t>0.06441093718823053</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0.057793257816708646</t>
+          <t>0.09209388057518571</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>0.9505277353581908</t>
+          <t>0.8840650607362517</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>1.2789301872253418</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>4.889300107955933</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>[0, 1, 3, 6, 7, 11, 12, 16, 17, 18, 20, 24, 27, 28, 29, 32, 33, 36, 37, 40, 41, 44]</t>
+          <t>[0, 1, 2, 4, 9, 10, 17, 18, 22, 23, 24, 25, 28, 29, 32, 33, 35, 37, 41, 42, 44]</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.6855158730158731</t>
+          <t>0.3631868131868132</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>0.0660964616037787</t>
+          <t>0.06297601211495978</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0.05717799404031846</t>
+          <t>0.07500799725905412</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>0.9515754862645721</t>
+          <t>0.9230926349956332</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>1.2753958702087402</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>4.695295095443726</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>[0, 2, 3, 8, 16, 19, 21, 23, 25, 26, 29, 30, 31, 32, 35, 37, 39, 42, 43, 44]</t>
+          <t>[1, 3, 6, 8, 10, 11, 17, 19, 20, 22, 23, 25, 32, 33, 36, 37, 39, 40, 41]</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.4194444444444444</t>
+          <t>1.1126373626373627</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>0.06227587019501425</t>
+          <t>0.061540545108246025</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0.05327794094363962</t>
+          <t>0.08409515529354837</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>0.9579561669912782</t>
+          <t>0.9033293261171744</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>1.2828056812286377</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>0</t>
+          <t>4.762543678283691</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>[1, 3, 9, 13, 15, 16, 18, 21, 22, 23, 25, 27, 28, 32, 33, 34, 37, 39, 41]</t>
+          <t>[0, 2, 4, 5, 9, 11, 12, 13, 15, 16, 19, 22, 23, 25, 28, 30, 35, 37]</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>0.7720238095238094</t>
+          <t>0.3906593406593407</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>0.06495343583878803</t>
+          <t>0.064602800791701</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0.05622391981694543</t>
+          <t>0.0859906585346685</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>0.9531780303470214</t>
+          <t>0.8989223021135115</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>1.274336576461792</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>3</t>
+          <t>4.645706653594971</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>[0, 3, 4, 9, 11, 14, 16, 17, 19, 21, 22, 25, 28, 29, 31, 33, 35, 36, 37, 43, 44]</t>
+          <t>[0, 1, 4, 5, 6, 7, 8, 13, 14, 18, 20, 23, 24, 25, 29, 30, 32, 33, 36, 39, 40, 42, 44]</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0.9805555555555556</t>
+          <t>0.610989010989011</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>0.06421163941513028</t>
+          <t>0.06745696486976875</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0.055799697749726686</t>
+          <t>0.08249895400949221</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>0.9538819292483853</t>
+          <t>0.9069642899071996</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>1.2582592964172363</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>3</t>
+          <t>4.703162431716919</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>[0, 1, 3, 4, 5, 8, 12, 14, 15, 16, 17, 23, 26, 28, 29, 30, 31, 33, 34, 35, 37, 38]</t>
+          <t>[1, 3, 8, 9, 10, 13, 14, 17, 19, 25, 28, 32, 33, 35, 39, 40, 42, 44]</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>0.7047619047619047</t>
+          <t>0.4758241758241758</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>0.06467096319278934</t>
+          <t>0.06276517720685944</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0.06001935228113339</t>
+          <t>0.09155838006954559</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>0.9466431666655672</t>
+          <t>0.8854094002258506</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>1.2732222080230713</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>4.707521677017212</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>[1, 3, 7, 13, 17, 18, 20, 22, 24, 25, 26, 28, 30, 31, 32, 33, 36, 37, 38, 39, 41, 42, 43, 44]</t>
+          <t>[1, 3, 11, 13, 14, 15, 16, 19, 23, 24, 32, 33, 37, 39, 40, 41, 42, 43, 44]</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>0.9859126984126985</t>
+          <t>0.7186813186813187</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>0.06541713083340572</t>
+          <t>0.06367179695177375</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0.06144482262138261</t>
+          <t>0.08769107769546325</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>0.9440786009741717</t>
+          <t>0.8948852632128685</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>1.2760262489318848</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>4.9168782234191895</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>[3, 4, 10, 12, 13, 14, 16, 18, 19, 20, 22, 23, 25, 29, 31, 32, 33, 40, 43, 44]</t>
+          <t>[0, 1, 4, 6, 7, 13, 16, 22, 23, 24, 25, 26, 29, 30, 33, 36, 37, 40]</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>0.6085317460317461</t>
+          <t>0.3247252747252747</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>0.06370945423598276</t>
+          <t>0.0666217187378232</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0.05841700075285972</t>
+          <t>0.08634660374972104</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>0.9494540981698736</t>
+          <t>0.8980837788017555</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>1.266319990158081</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>4.376033067703247</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>[1, 3, 4, 13, 17, 18, 20, 23, 25, 26, 28, 29, 31, 32, 33, 34, 40, 43, 44]</t>
+          <t>[0, 1, 2, 3, 4, 5, 7, 8, 10, 11, 12, 14, 15, 19, 25, 29, 30, 32, 33, 34, 35, 36, 37, 41, 42]</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>0.42896825396825394</t>
+          <t>1.023076923076923</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>0.06194326935939666</t>
+          <t>0.06682637379176867</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0.05737801375877592</t>
+          <t>0.07811484653471679</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>0.9512360969847848</t>
+          <t>0.9165896468391637</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>1.2838871479034424</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>0</t>
+          <t>4.422117710113525</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>[1, 2, 3, 4, 5, 9, 14, 16, 22, 23, 25, 26, 29, 33, 34, 35, 38, 39, 44]</t>
+          <t>[3, 6, 8, 10, 11, 13, 14, 18, 19, 22, 24, 25, 29, 32, 33, 36, 37, 38, 40, 44]</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>0.40654761904761905</t>
+          <t>0.7543956043956044</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>0.06531581043779855</t>
+          <t>0.060572315653232886</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>0.05285969708794401</t>
+          <t>0.08208447534559239</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>0.9586136831443376</t>
+          <t>0.907896773241863</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>1.2640621662139893</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>3</t>
+          <t>4.473884582519531</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>[1, 3, 6, 7, 9, 13, 14, 18, 19, 20, 21, 23, 27, 28, 29, 30, 31, 32, 33, 35, 36, 37, 44]</t>
+          <t>[0, 1, 3, 5, 10, 11, 13, 14, 15, 16, 17, 25, 26, 27, 30, 32, 33, 36, 39, 40]</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.7537698412698413</t>
+          <t>0.6626373626373627</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>0.0636084240406997</t>
+          <t>0.0651747926435295</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0.04895675182358436</t>
+          <t>0.08378040468544883</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>0.9644996504423425</t>
+          <t>0.9040516082044804</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>1.2729847431182861</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>0</t>
+          <t>5.107267618179321</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 7, 8, 10, 11, 12, 13, 15, 19, 20, 25, 26, 27, 30, 31, 32, 35, 36, 44]</t>
+          <t>[1, 3, 8, 9, 11, 13, 17, 18, 28, 29, 30, 32, 35, 36, 37, 43, 44]</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.6172619047619048</t>
+          <t>0.5659340659340659</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0.06501374477628594</t>
+          <t>0.06650114077134477</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0.052044154034971424</t>
+          <t>0.07383950050400533</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>0.9598808848906313</t>
+          <t>0.925470142197479</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>1.269261121749878</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>3</t>
+          <t>5.17247462272644</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>[1, 3, 4, 5, 6, 10, 13, 16, 17, 19, 20, 21, 22, 24, 26, 29, 33, 34, 35, 36, 42, 43, 44]</t>
+          <t>[3, 6, 7, 12, 13, 14, 16, 17, 18, 20, 21, 23, 24, 26, 30, 33, 35, 37, 40, 42, 43, 44]</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0.6686507936507937</t>
+          <t>0.28626373626373625</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>0.06694520751057113</t>
+          <t>0.0668351101414161</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0.05103353831396667</t>
+          <t>0.08039466421164611</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>0.961423857353098</t>
+          <t>0.9116498597075475</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>1.2736032009124756</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>3</t>
+          <t>4.352313995361328</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>[1, 3, 5, 7, 8, 9, 10, 11, 16, 17, 18, 19, 22, 23, 24, 25, 26, 27, 28, 30, 31, 32, 34, 35, 36, 37, 39, 40, 42, 43, 44]</t>
+          <t>[0, 2, 5, 8, 10, 12, 13, 18, 20, 22, 24, 25, 26, 28, 29, 30, 32, 33, 35, 36, 37, 38, 41, 42]</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>24</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>1.4420634920634923</t>
+          <t>0.8483516483516483</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>0.06577246233010342</t>
+          <t>0.06615524887472798</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>0.05415973266434535</t>
+          <t>0.07875194998226713</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>0.956552933146692</t>
+          <t>0.9152235113451005</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>1.268390417098999</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>3</t>
+          <t>4.951418399810791</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>[1, 3, 5, 8, 9, 12, 13, 14, 17, 21, 22, 24, 25, 26, 27, 28, 29, 32, 33, 34, 35, 36, 37, 38, 39, 40, 44]</t>
+          <t>[2, 3, 6, 7, 8, 10, 11, 13, 18, 20, 23, 25, 26, 27, 28, 29, 32, 33, 35, 36, 38, 44]</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>1.0861111111111112</t>
+          <t>0.8137362637362637</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>0.06542521038931494</t>
+          <t>0.06537461288120533</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0.054879412651675716</t>
+          <t>0.07433186281683428</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>0.9553906035324456</t>
+          <t>0.9244728971868214</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>1.2802486419677734</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>3</t>
+          <t>4.703982591629028</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>[0, 2, 3, 4, 6, 10, 11, 19, 25, 26, 27, 31, 35, 37, 41, 44]</t>
+          <t>[0, 1, 2, 11, 14, 17, 18, 19, 24, 25, 27, 32, 33, 37, 39]</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>0.2793650793650793</t>
+          <t>0.4065934065934066</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0.06253429814630146</t>
+          <t>0.060659437786798276</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0.044586939521459784</t>
+          <t>0.07852822544631137</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>0.9705542402424002</t>
+          <t>0.9157045061581912</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>1.2815883159637451</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>0</t>
+          <t>5.042164087295532</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>[0, 2, 3, 4, 6, 16, 19, 25, 26, 27, 28, 31, 32, 35, 37, 41, 44]</t>
+          <t>[2, 8, 10, 15, 21, 24, 25, 26, 30, 33, 34, 35, 37, 41, 44]</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>0.5777777777777777</t>
+          <t>0.18406593406593408</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>0.06323405906974233</t>
+          <t>0.06593757829683011</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>0.053153591843763635</t>
+          <t>0.07347938490609802</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>0.9581521960257738</t>
+          <t>0.926195334439235</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>1.2651863098144531</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>0</t>
+          <t>4.677213907241821</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>[0, 2, 5, 9, 12, 13, 15, 16, 17, 18, 19, 22, 26, 28, 29, 31, 32, 33, 34, 36, 37, 44]</t>
+          <t>[3, 5, 6, 10, 12, 13, 15, 18, 22, 24, 25, 28, 29, 32, 35, 36, 37, 42, 43, 44]</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>0.8412698412698412</t>
+          <t>0.5956043956043956</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>0.06485837261212293</t>
+          <t>0.06312183014870716</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>0.05614646740391004</t>
+          <t>0.07110944451730747</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>0.9533069426207417</t>
+          <t>0.9308794214763955</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>1.269101619720459</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>3</t>
+          <t>4.6546361446380615</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>[1, 3, 5, 9, 12, 13, 14, 18, 20, 22, 25, 26, 28, 31, 36, 37, 39, 41, 42, 44]</t>
+          <t>[0, 1, 2, 8, 9, 13, 17, 20, 21, 22, 23, 24, 25, 30, 31, 32, 33, 35, 42, 44]</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1577,39 +1442,34 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>0.892063492063492</t>
+          <t>0.15824175824175823</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>0.06567615425842488</t>
+          <t>0.06464567701346474</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>0.051018304636272487</t>
+          <t>0.083896582009403</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>0.9614468841246873</t>
+          <t>0.9037853226412689</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>1.2693910598754883</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>3</t>
+          <t>4.8539628982543945</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>[0, 1, 3, 4, 7, 8, 12, 14, 16, 17, 21, 23, 25, 26, 28, 31, 32, 35, 37, 39, 41, 44]</t>
+          <t>[1, 3, 5, 6, 9, 13, 17, 20, 21, 23, 25, 26, 27, 29, 32, 33, 35, 37, 38, 41, 43, 44]</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1619,123 +1479,108 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>0.930952380952381</t>
+          <t>0.42472527472527477</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>0.06094260915650627</t>
+          <t>0.06493689309933387</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>0.052565545869051294</t>
+          <t>0.07476882829987523</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>0.959073010912615</t>
+          <t>0.9235823035637635</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>1.2601842880249023</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>0</t>
+          <t>5.276846170425415</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>[1, 4, 7, 9, 10, 11, 13, 16, 18, 20, 21, 25, 28, 32, 33, 36, 41, 44]</t>
+          <t>[1, 2, 3, 5, 6, 7, 11, 12, 13, 22, 23, 25, 28, 29, 30, 32, 33, 35, 37, 39, 40, 42, 44]</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>0.5275793650793651</t>
+          <t>0.8236263736263736</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>0.06535612847556736</t>
+          <t>0.0647876280065796</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>0.06130780186008223</t>
+          <t>0.0803536748516372</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>0.9443277301553635</t>
+          <t>0.9117399276878102</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>1.2669563293457031</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>3.081737995147705</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>[2, 3, 4, 5, 8, 13, 14, 15, 16, 17, 19, 22, 26, 28, 31, 32, 35, 36, 37, 38, 39, 41, 42, 44]</t>
+          <t>[1, 2, 7, 8, 9, 10, 13, 14, 15, 17, 19, 23, 27, 28, 32, 33, 35, 36, 37, 41, 44]</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>1.2061507936507936</t>
+          <t>0.6956043956043956</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>0.06440480387174558</t>
+          <t>0.06482557937225548</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>0.05138202931042423</t>
+          <t>0.07701329792395538</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>0.9608952113209938</t>
+          <t>0.9189255081697103</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>1.2669281959533691</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>0</t>
+          <t>3.0866448879241943</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>[1, 3, 4, 5, 9, 10, 16, 20, 21, 23, 25, 27, 32, 33, 37, 42, 43, 44]</t>
+          <t>[3, 5, 8, 10, 11, 14, 16, 17, 25, 27, 29, 30, 33, 35, 37, 38, 40, 43]</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1745,753 +1590,663 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>0.46706349206349207</t>
+          <t>0.5620879120879121</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>0.06322573524632817</t>
+          <t>0.06343319081927198</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0.06143222107549559</t>
+          <t>0.08114024540269213</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>0.9441015361470231</t>
+          <t>0.9100035401831797</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>1.2622671127319336</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>3.3076634407043457</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>[2, 3, 4, 8, 13, 22, 25, 28, 31, 32, 35, 36, 43, 44]</t>
+          <t>[0, 1, 5, 6, 8, 10, 11, 12, 13, 15, 16, 20, 23, 26, 28, 33, 35, 36, 41, 42, 44]</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>0.3238095238095238</t>
+          <t>0.5983516483516484</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>0.06359627404428718</t>
+          <t>0.06643314345278259</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>0.04934365024187669</t>
+          <t>0.09194694393841812</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>0.9639363245845667</t>
+          <t>0.8844347161385699</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>1.2678642272949219</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>0</t>
+          <t>3.3168203830718994</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>[1, 3, 4, 5, 7, 10, 11, 13, 14, 15, 16, 17, 18, 19, 21, 22, 24, 25, 26, 27, 30, 33, 34, 35, 36, 44]</t>
+          <t>[0, 1, 3, 6, 8, 9, 13, 23, 24, 25, 28, 29, 32, 33, 36, 39, 44]</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>0.7289682539682539</t>
+          <t>0.7142857142857143</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>0.06577002763027409</t>
+          <t>0.06150610999889006</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0.06533974408486454</t>
+          <t>0.08150970315014044</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>0.9367643049343136</t>
+          <t>0.9091821084041624</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>1.2558071613311768</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>3.1727609634399414</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>[3, 4, 5, 13, 15, 20, 23, 24, 26, 27, 29, 30, 32, 33, 34, 37, 43, 44]</t>
+          <t>[1, 3, 5, 7, 11, 13, 14, 16, 18, 19, 21, 22, 23, 24, 25, 27, 28, 32, 33, 35, 36, 40, 41, 43]</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>24</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>0.30158730158730157</t>
+          <t>1.0225274725274724</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>0.06155499803062381</t>
+          <t>0.06437186283246177</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>0.05371214148856</t>
+          <t>0.07085928007225999</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>0.9572680832048451</t>
+          <t>0.931364901157588</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>1.264878273010254</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>0</t>
+          <t>3.1720948219299316</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>[1, 4, 5, 7, 16, 17, 23, 26, 29, 30, 31, 35, 36, 38, 39, 40, 41, 44]</t>
+          <t>[0, 2, 5, 7, 8, 9, 13, 16, 17, 18, 19, 21, 25, 26, 32, 35, 36, 37, 38, 39, 41, 42, 43]</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>0.37857142857142856</t>
+          <t>0.8098901098901099</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>0.06401593294236987</t>
+          <t>0.06784565708188765</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>0.05331149828902755</t>
+          <t>0.08659558050790157</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>0.9579031873255849</t>
+          <t>0.8974951892616511</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>1.2710957527160645</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>0</t>
+          <t>3.1540448665618896</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>[1, 2, 3, 5, 7, 11, 13, 14, 17, 19, 22, 24, 25, 26, 28, 31, 33, 34, 35, 37, 43, 44]</t>
+          <t>[1, 6, 8, 9, 10, 13, 23, 24, 25, 26, 29, 32, 33, 35, 36, 39, 43, 44]</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>0.8761904761904762</t>
+          <t>0.573076923076923</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>0.0634430032226572</t>
+          <t>0.0656917624034324</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>0.055560561791677586</t>
+          <t>0.08306151036760316</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>0.9542763707078785</t>
+          <t>0.9056911519520567</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>1.2611804008483887</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>0</t>
+          <t>3.2241601943969727</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>[1, 10, 11, 12, 17, 19, 21, 25, 26, 28, 29, 31, 32, 34, 35, 37, 40, 41, 42]</t>
+          <t>[0, 1, 3, 8, 11, 15, 16, 21, 24, 27, 30, 33, 35, 36, 39, 43, 44]</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>0.7464285714285714</t>
+          <t>0.5631868131868132</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>0.06505556064667542</t>
+          <t>0.06686314157789584</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>0.056712472079576644</t>
+          <t>0.0871525485827826</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>0.9523607851517728</t>
+          <t>0.8961723617109878</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>1.2669382095336914</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>3.1590774059295654</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>[1, 2, 3, 4, 10, 11, 14, 15, 16, 17, 18, 19, 20, 26, 32, 33, 34, 36, 37, 40, 42, 44]</t>
+          <t>[0, 1, 3, 4, 5, 6, 7, 10, 11, 12, 13, 14, 17, 18, 19, 20, 21, 25, 26, 27, 32, 33, 35, 36, 37, 39, 40, 42, 43, 44]</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>30</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>0.8174603174603174</t>
+          <t>0.9670329670329669</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>0.06434878469732604</t>
+          <t>0.06747926108208971</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>0.060531358095589786</t>
+          <t>0.07225470906738157</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>0.9457289437454532</t>
+          <t>0.9286350270308125</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>1.2628369331359863</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>3.1304092407226562</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>[3, 8, 11, 19, 21, 25, 26, 27, 28, 31, 33, 35, 36, 37, 42]</t>
+          <t>[0, 1, 7, 8, 13, 15, 18, 19, 21, 23, 24, 30, 32, 35, 36, 37, 43]</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>0.591468253968254</t>
+          <t>0.41648351648351645</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>0.062263719593936194</t>
+          <t>0.06222807298651577</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>0.05169998620360711</t>
+          <t>0.08073117835270618</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>0.9604097455832669</t>
+          <t>0.9109086837679784</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>1.255985975265503</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>0</t>
+          <t>3.1284637451171875</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>[0, 3, 10, 19, 22, 23, 26, 27, 30, 32, 34, 36, 39, 40, 41, 44]</t>
+          <t>[9, 15, 19, 22, 23, 25, 29, 30, 32, 34, 35, 36, 39, 41, 44]</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>0.3626984126984127</t>
+          <t>0.4368131868131868</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>0.06625969217784841</t>
+          <t>0.06570279195279123</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>0.05670962256307009</t>
+          <t>0.0687074010807991</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>0.9523655722934278</t>
+          <t>0.935470271958469</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>1.2624633312225342</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>3</t>
+          <t>3.1732237339019775</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>[1, 3, 7, 9, 10, 12, 13, 14, 23, 26, 29, 30, 31, 32, 33, 35, 36, 37, 38, 39, 41, 43, 44]</t>
+          <t>[1, 4, 6, 7, 9, 11, 15, 19, 22, 25, 26, 32, 33, 34, 35, 37, 39, 43, 44]</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>0.7440476190476191</t>
+          <t>0.7873626373626375</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>0.06367557298161655</t>
+          <t>0.060462558653865475</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>0.05794314685474205</t>
+          <t>0.081120796733182</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>0.950270786141795</t>
+          <t>0.9100466778795852</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>1.2679212093353271</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>3.141357898712158</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>[1, 3, 4, 5, 6, 7, 12, 13, 16, 17, 18, 20, 22, 23, 24, 25, 26, 28, 29, 31, 32, 34, 35, 38, 39, 44]</t>
+          <t>[6, 7, 8, 9, 10, 13, 22, 23, 28, 31, 33, 36, 38, 42, 44]</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>0.6371031746031746</t>
+          <t>0.3098901098901099</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>0.06542043741831807</t>
+          <t>0.06490767112273024</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>0.05681184105944044</t>
+          <t>0.07392875191153161</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>0.9521936964239123</t>
+          <t>0.925289861593982</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>1.2537691593170166</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>3.1258676052093506</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>[0, 1, 3, 5, 10, 12, 13, 17, 19, 21, 22, 24, 25, 28, 29, 31, 33, 36, 38, 40, 42, 44]</t>
+          <t>[1, 2, 4, 5, 11, 14, 15, 16, 20, 21, 23, 24, 25, 36, 37, 40]</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>0.7182539682539683</t>
+          <t>0.41373626373626377</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>0.06410146383651864</t>
+          <t>0.065253742344114</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>0.0573775908153525</t>
+          <t>0.09963608978296375</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>0.9512368158767338</t>
+          <t>0.8642980329758267</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>1.2920811176300049</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>3.1730520725250244</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>[1, 2, 3, 13, 14, 18, 19, 24, 26, 30, 32, 34, 36, 39, 40, 42, 43]</t>
+          <t>[0, 1, 3, 4, 6, 9, 14, 17, 18, 22, 23, 25, 26, 32, 35, 36, 37, 39, 40, 42, 43, 44]</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>0.4728174603174603</t>
+          <t>0.7956043956043957</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>0.06644436521910473</t>
+          <t>0.06448271433851631</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>0.06033115291468354</t>
+          <t>0.08393066126087038</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>0.9460873489957189</t>
+          <t>0.9037071409069359</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>1.265805721282959</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>3.183032512664795</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 7, 8, 11, 15, 16, 17, 21, 22, 23, 25, 26, 28, 29, 30, 32, 34, 35, 36, 38, 39, 41, 42, 44]</t>
+          <t>[0, 3, 4, 10, 11, 12, 19, 20, 22, 23, 25, 28, 29, 30, 32, 33, 34, 35, 36, 37, 39, 40, 42]</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>1.0162698412698412</t>
+          <t>0.7725274725274726</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>0.06719713325750588</t>
+          <t>0.06424064405599579</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>0.0568892732983871</t>
+          <t>0.06601435519525883</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>0.9520632915041046</t>
+          <t>0.940429730695448</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>1.2573790550231934</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>3</t>
+          <t>4.301560401916504</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>[1, 2, 4, 9, 10, 14, 21, 23, 26, 28, 29, 32, 33, 34, 35, 37, 39, 44]</t>
+          <t>[2, 4, 5, 9, 10, 12, 14, 15, 18, 19, 25, 29, 33, 37, 38, 39, 43]</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>0.6500000000000001</t>
+          <t>0.3549450549450549</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>0.06389261347301288</t>
+          <t>0.06694188290433374</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>0.05725451410150043</t>
+          <t>0.09270361489934684</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>0.9514457885976558</t>
+          <t>0.8825248167670944</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>1.2517006397247314</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>4.374225378036499</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>[0, 1, 3, 4, 15, 17, 18, 22, 25, 26, 28, 29, 30, 34, 35, 36, 37, 41, 42, 44]</t>
+          <t>[0, 1, 2, 4, 6, 7, 8, 9, 11, 12, 13, 15, 19, 20, 23, 26, 32, 33, 35, 37, 38, 39, 42, 44]</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>24</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>0.7057539682539683</t>
+          <t>0.971978021978022</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>0.06539769381933318</t>
+          <t>0.06324031025224522</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>0.06337449924211284</t>
+          <t>0.08626563412944024</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>0.9405110203865574</t>
+          <t>0.898274828553619</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>1.2590696811676025</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>4.3328893184661865</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>[1, 3, 4, 7, 14, 17, 18, 21, 26, 27, 33, 34, 37, 39]</t>
+          <t>[0, 3, 8, 9, 14, 15, 16, 17, 18, 19, 23, 24, 25, 26, 28, 32, 33, 34, 36, 39, 44]</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>0.3466269841269841</t>
+          <t>0.4423076923076923</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>0.06391457631546672</t>
+          <t>0.06336747982540465</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>0.06626376564941397</t>
+          <t>0.07952030059754446</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>0.9349631253462719</t>
+          <t>0.9135611822219695</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>1.2643940448760986</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>4.372513294219971</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>[1, 4, 7, 8, 9, 10, 12, 13, 17, 18, 19, 20, 22, 24, 25, 26, 27, 28, 29, 30, 31, 32, 33, 36, 37, 44]</t>
+          <t>[0, 2, 3, 4, 5, 7, 8, 10, 11, 13, 15, 16, 18, 22, 23, 24, 25, 27, 28, 32, 33, 35, 36, 40, 41, 44]</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2501,501 +2256,441 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>1.0956349206349207</t>
+          <t>1.0587912087912088</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>0.0634639745980394</t>
+          <t>0.06778526873234608</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>0.048037975638971685</t>
+          <t>0.07711566171309357</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>0.9658196241928659</t>
+          <t>0.9187098413209053</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>1.2599895000457764</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>0</t>
+          <t>4.691550016403198</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>[0, 3, 4, 6, 12, 16, 19, 21, 22, 24, 25, 26, 27, 28, 29, 32, 33, 34, 35, 36, 37, 38, 39, 40, 41, 43, 44]</t>
+          <t>[1, 2, 3, 8, 9, 14, 17, 18, 19, 20, 21, 22, 23, 25, 28, 29, 30, 33, 35, 36, 37, 40, 41]</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>1.1686507936507935</t>
+          <t>0.6593406593406593</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>0.06784502400069267</t>
+          <t>0.06491662830313885</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>0.05805172324680394</t>
+          <t>0.08319746275356772</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>0.950084241994746</t>
+          <t>0.9053821759709767</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>1.2714250087738037</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>4.56928014755249</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>[4, 5, 9, 20, 23, 25, 28, 29, 30, 31, 34, 35, 37, 38, 40, 41, 44]</t>
+          <t>[0, 1, 3, 10, 11, 12, 17, 19, 22, 23, 24, 25, 26, 30, 32, 33, 35, 36, 40, 41, 43, 44]</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>0.35079365079365077</t>
+          <t>0.6291208791208791</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>0.06612676924574104</t>
+          <t>0.06556290558260183</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>0.05739837843103944</t>
+          <t>0.0819911827884951</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>0.9512014761581894</t>
+          <t>0.90810601287226</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>1.2778847217559814</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>4.469821214675903</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>[1, 2, 3, 4, 14, 15, 16, 17, 18, 20, 24, 25, 26, 28, 29, 32, 34, 36, 37, 38, 39, 40, 41, 43, 44]</t>
+          <t>[0, 7, 8, 9, 12, 14, 19, 20, 21, 23, 25, 29, 30, 31, 32, 33, 36, 38, 40]</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>1.038095238095238</t>
+          <t>0.32417582417582413</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>0.06460824287558989</t>
+          <t>0.06373125849855825</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>0.05765433426819581</t>
+          <t>0.07980586937087673</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>0.9507652925513987</t>
+          <t>0.912939239164146</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>1.260540246963501</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>4.277544975280762</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>[2, 3, 4, 10, 11, 12, 13, 14, 15, 19, 20, 24, 25, 26, 31, 32, 33, 36, 37, 38, 41, 42, 43, 44]</t>
+          <t>[0, 1, 3, 4, 5, 6, 19, 20, 22, 23, 25, 26, 27, 32, 33, 36, 40, 41, 42, 44]</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>0.9412698412698413</t>
+          <t>0.5087912087912088</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>0.06596393736988385</t>
+          <t>0.06310040509089478</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>0.060783067187612706</t>
+          <t>0.07481347958982817</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>0.945276651870146</t>
+          <t>0.9234910043512067</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>1.2635550498962402</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>3.6851720809936523</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>[1, 3, 4, 9, 10, 12, 14, 16, 23, 24, 26, 27, 29, 30, 32, 35, 37, 39, 41, 42, 44]</t>
+          <t>[1, 7, 9, 15, 19, 23, 24, 25, 29, 32, 33, 34, 37, 38]</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>0.6103174603174604</t>
+          <t>0.21703296703296704</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>0.06606236222290238</t>
+          <t>0.06727862827599525</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>0.060392049430884956</t>
+          <t>0.07978428618548146</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>0.9459784583348945</t>
+          <t>0.9129863232812897</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>1.2765419483184814</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>3.5352420806884766</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>[0, 1, 3, 11, 12, 13, 15, 19, 24, 25, 29, 30, 32, 33, 34, 35, 36, 37, 43]</t>
+          <t>[0, 1, 3, 5, 6, 7, 8, 10, 11, 12, 13, 16, 21, 22, 23, 24, 25, 28, 30, 33, 36, 37, 39, 44]</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>24</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>0.5996031746031746</t>
+          <t>0.939010989010989</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>0.06381002582933427</t>
+          <t>0.06422617542545724</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>0.06258851915127499</t>
+          <t>0.08080576965609704</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>0.9419774527694003</t>
+          <t>0.9107439764628432</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>1.261155605316162</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>3.1481592655181885</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>[3, 4, 5, 9, 10, 11, 17, 18, 19, 21, 22, 23, 24, 25, 26, 27, 29, 31, 32, 33, 35, 36, 37, 41, 43, 44]</t>
+          <t>[0, 2, 8, 10, 15, 23, 27, 29, 33, 37, 38, 39, 44]</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>0.8876984126984127</t>
+          <t>0.10989010989010989</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>0.06374080968636449</t>
+          <t>0.06584798451822611</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>0.05486828651663215</t>
+          <t>0.08345602717605703</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>0.9554086897266256</t>
+          <t>0.9047931479269491</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>1.2657256126403809</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>0</t>
+          <t>3.092907190322876</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>[2, 3, 4, 10, 12, 13, 14, 15, 19, 20, 21, 24, 27, 28, 29, 32, 33, 34, 37, 41, 43, 44]</t>
+          <t>[2, 3, 5, 7, 10, 11, 13, 17, 18, 19, 20, 23, 25, 27, 28, 30, 33, 35, 36, 37, 38, 41, 43, 44]</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>24</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>0.6297619047619047</t>
+          <t>0.7054945054945054</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>0.06556785457376409</t>
+          <t>0.06656940624348434</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>0.05856343053629841</t>
+          <t>0.07111643094985173</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>0.9492003808725364</t>
+          <t>0.930865838752326</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>1.2800374031066895</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>3.045119047164917</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>[1, 3, 4, 5, 9, 13, 15, 16, 17, 18, 19, 20, 22, 23, 25, 26, 27, 28, 29, 32, 33, 34, 36, 37, 38, 39, 40, 41, 44]</t>
+          <t>[0, 7, 8, 9, 10, 11, 15, 17, 18, 24, 25, 26, 27, 28, 29, 30, 32, 33, 36, 38, 40, 42, 44]</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>1.2555555555555555</t>
+          <t>0.7340659340659341</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>0.06587534450415228</t>
+          <t>0.067655757006323</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>0.05963154306713407</t>
+          <t>0.07470769163901066</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>0.9473304590225041</t>
+          <t>0.9237072222722195</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>1.2638368606567383</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>3.117157459259033</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>[3, 6, 11, 12, 16, 19, 20, 22, 28, 29, 31, 33, 37, 38]</t>
+          <t>[0, 1, 7, 8, 9, 13, 15, 19, 24, 25, 32, 33, 34, 36, 37, 41, 43, 44]</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>0.5095238095238095</t>
+          <t>0.48791208791208796</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>0.06796230578211637</t>
+          <t>0.06541228665831059</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>0.05438743367500948</t>
+          <t>0.08361110050894689</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>0.9561868406000815</t>
+          <t>0.9044390030862178</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>1.2691521644592285</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>3</t>
+          <t>3.1080713272094727</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>[3, 4, 6, 7, 9, 10, 11, 16, 18, 19, 23, 25, 27, 28, 29, 31, 32, 34, 36, 37, 42]</t>
+          <t>[0, 7, 9, 11, 12, 17, 18, 19, 23, 25, 29, 32, 33, 35, 37, 38, 39, 40]</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>0.8299603174603174</t>
+          <t>0.4752747252747253</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>0.06562584323324154</t>
+          <t>0.0604546659869431</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>0.05471452362979757</t>
+          <t>0.08165112419200973</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>0.9556582649081444</t>
+          <t>0.9088666931277826</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>1.2746775150299072</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>3</t>
+          <t>3.1263797283172607</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>[0, 1, 3, 7, 12, 13, 14, 15, 19, 24, 25, 27, 29, 30, 32, 33, 36, 38, 39, 42, 44]</t>
+          <t>[1, 5, 8, 9, 11, 12, 13, 15, 21, 23, 25, 27, 28, 29, 30, 32, 33, 35, 36, 38, 39]</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -3005,291 +2700,256 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>0.6557539682539683</t>
+          <t>0.8697802197802198</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>0.0647339115238357</t>
+          <t>0.06443093369766581</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>0.06843217175044779</t>
+          <t>0.07180922642764272</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>0.930636965561861</t>
+          <t>0.9295123082886214</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>1.265700340270996</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>3.0927340984344482</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>[1, 4, 10, 19, 20, 24, 26, 27, 33, 34, 36, 37, 39, 43, 44]</t>
+          <t>[0, 1, 5, 8, 9, 11, 12, 14, 16, 18, 19, 20, 22, 23, 24, 25, 27, 30, 32, 33, 35, 36, 38, 44]</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>24</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>0.403968253968254</t>
+          <t>0.7664835164835164</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>0.06198771941659498</t>
+          <t>0.061478350638756285</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>0.07145630454873823</t>
+          <t>0.07517081649962726</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>0.9243709677865326</t>
+          <t>0.9227583882506927</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>1.263779878616333</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>3.0997791290283203</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>[0, 9, 11, 17, 19, 20, 21, 22, 25, 26, 28, 33, 34, 35, 36, 37, 39, 41, 43, 44]</t>
+          <t>[0, 2, 3, 4, 5, 6, 8, 9, 11, 15, 19, 22, 23, 25, 29, 30, 32, 33, 38, 43, 44]</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>1.0549603174603175</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>0.06615522179938037</t>
+          <t>0.06533282821856504</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>0.06057152292827567</t>
+          <t>0.10585980591713631</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>0.9456568980769476</t>
+          <t>0.8468154450697232</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>1.2789955139160156</t>
-        </is>
-      </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>3.0836737155914307</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>[1, 4, 9, 10, 11, 14, 15, 16, 17, 18, 19, 25, 28, 30, 31, 32, 33, 34, 35, 36, 37, 40, 43, 44]</t>
+          <t>[1, 3, 4, 6, 10, 13, 14, 15, 17, 19, 27, 30, 32, 33, 36, 39, 40, 41, 42, 44]</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>0.8938492063492064</t>
+          <t>0.6725274725274726</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>0.06508951862947562</t>
+          <t>0.06571601443313296</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>0.058428534060002334</t>
+          <t>0.07672447333867058</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>0.9494341375779116</t>
+          <t>0.9195324785963153</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>1.2751238346099854</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>3.0929131507873535</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>[0, 1, 3, 5, 7, 10, 11, 16, 17, 18, 19, 20, 21, 23, 25, 26, 27, 28, 29, 30, 31, 32, 33, 34, 35, 36, 37, 41, 44]</t>
+          <t>[2, 5, 7, 9, 10, 11, 13, 14, 16, 18, 19, 23, 25, 30, 33, 35, 37, 38, 39, 42]</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>1.0432539682539683</t>
+          <t>0.5313186813186813</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>0.0650459984334117</t>
+          <t>0.06459145881535873</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>0.05809916940739289</t>
+          <t>0.08792597574590538</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>0.9500026155155311</t>
+          <t>0.8943213673728452</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>1.258465051651001</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>3.0801491737365723</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>[2, 9, 15, 16, 17, 19, 20, 22, 24, 26, 30, 31, 32, 33, 34, 35, 36, 37, 40]</t>
+          <t>[0, 1, 3, 4, 5, 6, 7, 8, 9, 10, 11, 12, 14, 17, 18, 21, 22, 23, 24, 26, 27, 29, 32, 33, 35, 37, 38, 42, 43, 44]</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>30</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>0.731547619047619</t>
+          <t>1.0642857142857143</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>0.06481976150655702</t>
+          <t>0.06455195926512554</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>0.06068636292755381</t>
+          <t>0.07546370627104025</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>0.9454506401676226</t>
+          <t>0.9221552991035453</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>1.2698814868927002</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>3.0609333515167236</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>[3, 6, 14, 16, 19, 20, 23, 24, 25, 27, 28, 29, 31, 33, 35, 36, 37, 42, 43, 44]</t>
+          <t>[0, 1, 2, 5, 8, 9, 10, 11, 12, 14, 16, 19, 20, 21, 23, 32, 33, 35, 38]</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>0.6738095238095239</t>
+          <t>0.5263736263736264</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>0.06486934250103302</t>
+          <t>0.06385579227292829</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>0.05342827270770347</t>
+          <t>0.09741882144281744</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>0.9577185661895781</t>
+          <t>0.8702705625842713</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>1.2693321704864502</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>3</t>
+          <t>3.075049877166748</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>[3, 4, 9, 11, 12, 13, 15, 17, 23, 26, 28, 29, 30, 31, 33, 34, 35, 36, 37, 38, 39, 44]</t>
+          <t>[0, 3, 5, 6, 7, 9, 10, 11, 15, 19, 20, 23, 25, 29, 30, 32, 33, 35, 36, 39, 41, 44]</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -3299,39 +2959,34 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>0.6698412698412698</t>
+          <t>0.7368131868131869</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>0.06364544944151547</t>
+          <t>0.06317889386729245</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>0.05570566669781735</t>
+          <t>0.0819968544511118</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>0.9540372303349414</t>
+          <t>0.9080932990730383</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>1.276669979095459</t>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>0</t>
+          <t>3.1433677673339844</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>[0, 1, 3, 4, 6, 10, 13, 16, 17, 23, 24, 26, 29, 31, 32, 35, 36, 37, 40, 41, 44]</t>
+          <t>[0, 3, 6, 8, 10, 11, 12, 17, 18, 23, 24, 26, 28, 30, 32, 33, 35, 37, 41, 43, 44]</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -3341,375 +2996,330 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>0.466468253968254</t>
+          <t>0.7115384615384616</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>0.06516232161060781</t>
+          <t>0.06456777927911247</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>0.05608024360119021</t>
+          <t>0.08119523578194691</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>0.9534170249952649</t>
+          <t>0.9098815140189664</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>1.2546899318695068</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>3</t>
+          <t>3.0904383659362793</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>[3, 9, 10, 12, 14, 15, 16, 19, 20, 21, 24, 25, 26, 27, 28, 29, 30, 33, 34, 35, 37, 41]</t>
+          <t>[1, 3, 5, 8, 17, 18, 22, 25, 29, 30, 33, 35, 37, 40, 42, 43]</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>0.6700396825396826</t>
+          <t>0.3478021978021978</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>0.0662113608563705</t>
+          <t>0.0644646271801275</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>0.05702281756157155</t>
+          <t>0.07772427358380124</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>0.9518379700745637</t>
+          <t>0.9174216623883293</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>1.2713944911956787</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>3.1085760593414307</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>[1, 2, 3, 4, 9, 10, 15, 16, 17, 19, 23, 26, 27, 28, 31, 33, 34, 36, 41, 42, 44]</t>
+          <t>[1, 2, 3, 7, 8, 9, 10, 11, 12, 13, 14, 15, 17, 19, 22, 25, 26, 29, 32, 33, 35, 37, 39, 41, 44]</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>0.6736111111111112</t>
+          <t>1.0994505494505495</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>0.06345997116753695</t>
+          <t>0.06278276841949848</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>0.05664424350350041</t>
+          <t>0.08024543701919934</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>0.9524753419851062</t>
+          <t>0.911977543325221</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>1.2636620998382568</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>0</t>
+          <t>3.0476975440979004</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>[2, 3, 5, 10, 19, 21, 22, 24, 25, 26, 29, 32, 33, 34, 35, 39, 43, 44]</t>
+          <t>[0, 6, 8, 10, 11, 12, 13, 14, 16, 21, 22, 23, 25, 27, 29, 30, 32, 33, 35, 36, 38, 40, 42]</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>0.3359126984126984</t>
+          <t>0.8027472527472528</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>0.06706088266505081</t>
+          <t>0.06536444709953489</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>0.06249263510131517</t>
+          <t>0.08062498218952509</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>0.9421550947832913</t>
+          <t>0.9111429162766151</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>1.31365966796875</t>
-        </is>
-      </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>3.140594244003296</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>[3, 4, 9, 10, 12, 14, 15, 21, 22, 23, 25, 26, 28, 30, 31, 32, 33, 34, 35, 37, 38, 40, 41, 43, 44]</t>
+          <t>[1, 2, 3, 4, 5, 11, 13, 16, 17, 19, 20, 24, 25, 27, 30, 32, 33, 35, 36, 37, 42, 43]</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>0.8851190476190477</t>
+          <t>0.7824175824175823</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>0.06616150569309319</t>
+          <t>0.06442026330313383</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>0.05877854144758722</t>
+          <t>0.06877598607561375</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>0.9488265085974126</t>
+          <t>0.9353413781293731</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>1.2931554317474365</t>
-        </is>
-      </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>3.1238315105438232</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>[0, 3, 6, 7, 9, 13, 15, 17, 19, 20, 23, 25, 27, 28, 29, 32, 33, 36, 37, 40, 44]</t>
+          <t>[0, 3, 6, 7, 8, 11, 14, 15, 18, 20, 23, 24, 25, 27, 28, 30, 32, 33, 35, 36, 37, 38, 40, 42, 43, 44]</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>26</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>0.7180555555555554</t>
+          <t>1.0593406593406594</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>0.06383404725164851</t>
+          <t>0.06297568884558188</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>0.051837732243649716</t>
+          <t>0.07689991031154014</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>0.9601985012092472</t>
+          <t>0.9191640663391926</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>1.3416051864624023</t>
-        </is>
-      </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>0</t>
+          <t>3.078333616256714</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>[1, 2, 9, 10, 12, 13, 17, 18, 22, 23, 25, 26, 27, 31, 32, 33, 34, 35, 37, 39, 40, 41, 42, 43, 44]</t>
+          <t>[0, 4, 5, 8, 11, 15, 18, 19, 21, 23, 25, 26, 29, 31, 32, 33, 35, 36, 38, 40, 42, 44]</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>0.6825396825396826</t>
+          <t>0.7258241758241759</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>0.06764168865924969</t>
+          <t>0.06607755169162574</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>0.06217319013786366</t>
+          <t>0.07901610643814758</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>0.9427449574361195</t>
+          <t>0.9146538285589383</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>1.4518835544586182</t>
-        </is>
-      </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>3.171093463897705</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>[5, 6, 8, 12, 16, 17, 19, 20, 21, 23, 24, 25, 26, 29, 31, 32, 36, 41, 42, 44]</t>
+          <t>[0, 6, 7, 11, 12, 13, 14, 17, 22, 23, 24, 25, 32, 33, 35, 37, 38, 39, 44]</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>0.5134920634920634</t>
+          <t>0.41923076923076924</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>0.06798041189728468</t>
+          <t>0.0661308238594411</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>0.05327099765284988</t>
+          <t>0.08302657391169063</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>0.9579671247547109</t>
+          <t>0.9057704696524417</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>1.3302855491638184</t>
-        </is>
-      </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>3</t>
+          <t>3.0830905437469482</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3, 4, 5, 7, 9, 12, 14, 16, 17, 18, 20, 24, 25, 26, 28, 29, 30, 32, 34, 35, 37, 40, 44]</t>
+          <t>[0, 1, 3, 4, 6, 7, 8, 9, 12, 13, 17, 19, 20, 22, 23, 30, 32, 33, 35, 37, 38, 40, 41, 42]</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>24</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>0.7075396825396825</t>
+          <t>0.895054945054945</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>0.06472004478888696</t>
+          <t>0.06421434036797233</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>0.0560712609060938</t>
+          <t>0.09105472464642228</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>0.9534319467260657</t>
+          <t>0.8866666403911955</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>1.4075260162353516</t>
-        </is>
-      </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>3</t>
+          <t>3.158674955368042</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>[0, 3, 4, 6, 9, 13, 14, 16, 19, 23, 24, 25, 26, 27, 28, 36, 37, 39, 42, 44]</t>
+          <t>[0, 4, 6, 10, 12, 15, 18, 22, 23, 24, 25, 26, 27, 28, 32, 35, 36, 37, 39, 44]</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3719,39 +3329,34 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>0.7331349206349207</t>
+          <t>0.5703296703296703</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>0.06482299337300859</t>
+          <t>0.06305481389323193</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>0.055330228590507596</t>
+          <t>0.06674895312584739</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>0.9546546908469495</t>
+          <t>0.939096575962469</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>1.3102238178253174</t>
-        </is>
-      </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>3</t>
+          <t>4.5005974769592285</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>[3, 6, 8, 9, 13, 18, 19, 21, 22, 23, 25, 26, 27, 28, 29, 30, 31, 32, 33, 36, 37, 39, 40, 44]</t>
+          <t>[0, 2, 3, 4, 6, 7, 8, 14, 15, 18, 19, 20, 22, 23, 24, 28, 29, 30, 32, 33, 35, 36, 37, 44]</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3761,39 +3366,34 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>0.9831349206349207</t>
+          <t>0.7571428571428571</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>0.0653893590903029</t>
+          <t>0.06541222741861043</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>0.05033775100204082</t>
+          <t>0.07972811906797352</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>0.9624685749582873</t>
+          <t>0.9131087931895304</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>1.3848681449890137</t>
-        </is>
-      </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>3</t>
+          <t>3.994688034057617</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>[0, 4, 7, 10, 12, 14, 16, 17, 19, 21, 22, 24, 26, 29, 31, 32, 35, 37, 39, 42, 44]</t>
+          <t>[1, 2, 3, 10, 11, 12, 13, 15, 17, 19, 21, 22, 25, 28, 31, 33, 35, 37, 39, 41, 43]</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3803,207 +3403,182 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>0.6103174603174604</t>
+          <t>0.8587912087912088</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>0.06295455295590319</t>
+          <t>0.06871467367413157</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>0.053397853332192186</t>
+          <t>0.07742268539736924</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>0.9577666983340549</t>
+          <t>0.9180612652311757</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>1.3827943801879883</t>
-        </is>
-      </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>0</t>
+          <t>4.5948145389556885</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>[1, 3, 5, 8, 12, 13, 15, 16, 17, 18, 20, 23, 26, 28, 29, 30, 31, 32, 33, 35, 37, 42, 43, 44]</t>
+          <t>[2, 3, 7, 9, 11, 13, 17, 18, 20, 23, 28, 32, 33, 37, 40]</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>0.7936507936507936</t>
+          <t>0.3505494505494505</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>0.06299380920278724</t>
+          <t>0.06629522705694497</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>0.05061569635364307</t>
+          <t>0.09288286413664353</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>0.9620529630264256</t>
+          <t>0.8820700837996416</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>1.399531602859497</t>
-        </is>
-      </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>0</t>
+          <t>4.867150068283081</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>[3, 5, 16, 17, 18, 23, 24, 25, 28, 29, 31, 35, 37, 38, 39, 40, 44]</t>
+          <t>[0, 1, 2, 4, 8, 10, 15, 17, 19, 23, 26, 29, 33, 35, 37, 40, 42, 43]</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>0.22103174603174602</t>
+          <t>0.5005494505494505</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>0.06652017022613292</t>
+          <t>0.06585798672536772</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>0.05913744109947918</t>
+          <t>0.0889836145188951</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>0.9481996737248267</t>
+          <t>0.891763714904779</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>1.3634817600250244</t>
-        </is>
-      </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>4.896909236907959</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>[1, 3, 4, 5, 11, 13, 16, 19, 20, 23, 26, 28, 30, 31, 32, 37, 41, 42, 43, 44]</t>
+          <t>[2, 3, 6, 10, 19, 21, 23, 24, 25, 27, 28, 29, 32, 33, 35, 37]</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>0.8154761904761905</t>
+          <t>0.40934065934065933</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>0.06713551976513477</t>
+          <t>0.06303159670793537</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>0.059342272267023065</t>
+          <t>0.07424135278483797</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>0.947840216287659</t>
+          <t>0.9246567160321203</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>1.3958687782287598</t>
-        </is>
-      </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>4.977302312850952</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>[0, 3, 4, 5, 9, 11, 13, 17, 19, 20, 22, 23, 26, 28, 32, 33, 34, 36, 37, 40, 41, 42, 44]</t>
+          <t>[0, 1, 2, 3, 6, 11, 12, 13, 14, 15, 17, 21, 25, 30, 32, 35, 36, 38, 39, 42, 44]</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>1.2069444444444444</t>
+          <t>0.682967032967033</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>0.06464073397319844</t>
+          <t>0.06564823492663754</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>0.05233140807146913</t>
+          <t>0.08760803672578006</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>0.9594367934469272</t>
+          <t>0.895084250314469</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>1.3833277225494385</t>
-        </is>
-      </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>3</t>
+          <t>4.879047155380249</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>[1, 3, 7, 13, 14, 15, 19, 20, 22, 23, 24, 25, 26, 31, 32, 33, 35, 37, 40, 42]</t>
+          <t>[0, 3, 11, 13, 18, 19, 21, 23, 25, 26, 29, 30, 33, 35, 36, 37, 38, 40, 42, 44]</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -4013,207 +3588,182 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>0.6867063492063492</t>
+          <t>0.5318681318681319</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>0.0663714002433454</t>
+          <t>0.06600542431511827</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>0.06182114362206177</t>
+          <t>0.07506279644199941</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>0.9433915181730977</t>
+          <t>0.9229802203088088</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>1.3627049922943115</t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>5.039904594421387</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>[1, 3, 4, 5, 6, 7, 9, 12, 14, 15, 16, 17, 18, 22, 25, 26, 27, 28, 29, 33, 35, 37, 38, 42, 44]</t>
+          <t>[4, 5, 8, 12, 15, 16, 18, 23, 25, 26, 28, 31, 32, 33, 34, 35, 40, 41, 42]</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>0.7914682539682539</t>
+          <t>0.46483516483516485</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>0.06586983504928015</t>
+          <t>0.0665216536938167</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>0.05221149028181999</t>
+          <t>0.0769816565811998</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>0.9596224821955528</t>
+          <t>0.9189921142979709</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>1.3796758651733398</t>
-        </is>
-      </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>3</t>
+          <t>3.1265416145324707</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>[0, 3, 4, 7, 8, 9, 12, 13, 17, 18, 19, 20, 22, 23, 24, 26, 28, 29, 31, 33, 36, 39, 41, 42, 43, 44]</t>
+          <t>[1, 2, 3, 10, 11, 13, 15, 17, 23, 26, 27, 32, 33, 36, 37, 42]</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>1.0327380952380951</t>
+          <t>0.40714285714285714</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>0.06745222515012295</t>
+          <t>0.06280413521627673</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>0.05314395552861307</t>
+          <t>0.07781705467832674</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>0.9581673679853615</t>
+          <t>0.9172243937316983</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>1.3893070220947266</t>
-        </is>
-      </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>3</t>
+          <t>3.0463924407958984</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>[2, 3, 4, 7, 8, 9, 10, 13, 14, 17, 24, 25, 26, 27, 29, 31, 32, 35, 37, 39, 42, 43, 44]</t>
+          <t>[0, 2, 3, 4, 5, 6, 10, 12, 16, 20, 21, 22, 23, 25, 26, 27, 29, 30, 32, 33, 35, 38, 40, 44]</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>0.5950396825396825</t>
+          <t>0.3934065934065934</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>0.0649177608670135</t>
+          <t>0.06569814126273384</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>0.05303491459390309</t>
+          <t>0.08327428226124091</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>0.9583388565255886</t>
+          <t>0.9052073665462026</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>1.386646032333374</t>
-        </is>
-      </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>3</t>
+          <t>3.1800544261932373</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>[1, 3, 4, 5, 8, 10, 11, 14, 20, 22, 23, 26, 28, 29, 32, 33, 34, 36, 37, 39, 40, 44]</t>
+          <t>[0, 1, 2, 5, 8, 9, 11, 13, 14, 16, 17, 20, 22, 23, 25, 26, 28, 30, 32, 33, 35, 36, 37, 41, 44]</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>1.0583333333333333</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>0.064983595817632</t>
+          <t>0.0632353037783744</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>0.055233403813484204</t>
+          <t>0.07838928337040485</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>0.9548132554490736</t>
+          <t>0.9160025347840044</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>1.3916449546813965</t>
-        </is>
-      </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>3</t>
+          <t>3.134972095489502</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>[0, 2, 3, 5, 14, 15, 17, 19, 21, 23, 24, 26, 27, 28, 29, 31, 32, 34, 35, 41, 44]</t>
+          <t>[1, 3, 6, 9, 13, 14, 15, 16, 18, 19, 21, 23, 24, 27, 29, 32, 33, 40, 42, 43, 44]</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -4223,165 +3773,145 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>0.46984126984126984</t>
+          <t>0.3835164835164835</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>0.06542465074758365</t>
+          <t>0.06525129698247714</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>0.05986145599062131</t>
+          <t>0.09661242536034853</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>0.9469235350427216</t>
+          <t>0.8724093758834568</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>1.392228603363037</t>
-        </is>
-      </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>3.2161529064178467</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>[0, 1, 5, 6, 7, 9, 11, 12, 13, 14, 15, 17, 18, 19, 20, 22, 23, 25, 26, 27, 28, 29, 30, 33, 34, 35, 37, 42, 44]</t>
+          <t>[0, 3, 5, 6, 8, 10, 12, 13, 14, 17, 19, 20, 21, 22, 23, 25, 26, 29, 32, 33, 36, 37, 39, 40, 42, 44]</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>26</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>1.1357142857142857</t>
+          <t>0.7796703296703297</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>0.06577496906140921</t>
+          <t>0.0636470034082546</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>0.05412738528839493</t>
+          <t>0.07909915826888574</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>0.9566048159327768</t>
+          <t>0.9144743238681865</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>1.3286514282226562</t>
-        </is>
-      </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>3</t>
+          <t>3.1605100631713867</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>[1, 2, 4, 5, 8, 11, 13, 16, 17, 18, 19, 20, 25, 28, 29, 30, 32, 33, 34, 35, 36, 37, 39, 40, 41, 42, 44]</t>
+          <t>[2, 3, 9, 12, 13, 16, 17, 19, 23, 25, 28, 29, 30, 32, 33, 35, 36, 37, 39, 40]</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>1.280357142857143</t>
+          <t>0.5164835164835164</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>0.06689297580780285</t>
+          <t>0.06369006605672461</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>0.05599022877694638</t>
+          <t>0.07291120617497024</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>0.9535664463530787</t>
+          <t>0.9273323094750949</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>1.3302786350250244</t>
-        </is>
-      </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>3</t>
+          <t>3.2082738876342773</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>[1, 5, 10, 12, 19, 20, 23, 24, 26, 28, 29, 31, 32, 34, 35, 41, 43, 44]</t>
+          <t>[0, 2, 3, 6, 8, 10, 11, 12, 13, 18, 19, 24, 25, 26, 27, 32, 33, 35, 37, 38, 40]</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>0.3478174603174603</t>
+          <t>0.8642857142857143</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>0.06309890765023453</t>
+          <t>0.06296802209013104</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>0.0604477489019275</t>
+          <t>0.0858663901377481</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>0.9458787644543842</t>
+          <t>0.899214233531976</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>1.314992904663086</t>
-        </is>
-      </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>3.1933534145355225</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 4, 7, 8, 9, 10, 13, 15, 17, 22, 23, 26, 28, 29, 30, 34, 35, 37, 39, 42]</t>
+          <t>[0, 1, 3, 6, 7, 10, 12, 16, 17, 19, 22, 23, 24, 25, 28, 29, 31, 32, 33, 35, 36, 41]</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -4391,39 +3921,34 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>0.7748015873015873</t>
+          <t>0.573076923076923</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>0.06739766905886112</t>
+          <t>0.06682172684778294</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>0.06046780164675281</t>
+          <t>0.07623488916089526</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>0.9458428504837464</t>
+          <t>0.920556139769564</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>1.3098065853118896</t>
-        </is>
-      </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>3.31980037689209</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>[7, 10, 13, 14, 19, 21, 22, 23, 26, 29, 31, 33, 37, 39, 40, 43]</t>
+          <t>[0, 8, 15, 20, 22, 23, 24, 25, 26, 27, 30, 32, 33, 36, 42, 44]</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -4433,123 +3958,108 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>0.35257936507936505</t>
+          <t>0.1813186813186813</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>0.06484036752654787</t>
+          <t>0.06216557255916335</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>0.04995134008650263</t>
+          <t>0.07448416089792367</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>0.9630425731440111</t>
+          <t>0.9241630861252395</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>1.3240602016448975</t>
-        </is>
-      </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>3</t>
+          <t>3.269693374633789</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 8, 12, 17, 21, 25, 26, 28, 29, 30, 31, 33, 35, 36, 37, 40, 41, 42, 44]</t>
+          <t>[1, 3, 6, 12, 14, 16, 17, 21, 22, 24, 25, 26, 30, 32, 33, 34, 35, 36, 37, 38, 40, 43, 44]</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>0.745436507936508</t>
+          <t>0.5879120879120879</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>0.06362625152365001</t>
+          <t>0.0644260791303652</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>0.053875287160121084</t>
+          <t>0.07776371466672836</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>0.9570081004614879</t>
+          <t>0.9173378325810778</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>1.3275964260101318</t>
-        </is>
-      </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>0</t>
+          <t>3.3453571796417236</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3, 5, 6, 10, 13, 15, 17, 18, 19, 23, 25, 26, 27, 28, 31, 32, 35, 37, 41, 44]</t>
+          <t>[1, 8, 12, 15, 19, 25, 27, 28, 31, 32, 33, 35, 38, 41]</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>0.7152777777777779</t>
+          <t>0.43956043956043955</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>0.06379542247931427</t>
+          <t>0.06330351754825163</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>0.053376624252909656</t>
+          <t>0.07466604566402883</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>0.9578002725633759</t>
+          <t>0.9237922577337587</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>1.3339009284973145</t>
-        </is>
-      </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>0</t>
+          <t>3.1631298065185547</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>[3, 15, 16, 19, 21, 23, 24, 25, 27, 28, 30, 33, 36, 38, 39, 41, 44]</t>
+          <t>[3, 4, 10, 12, 13, 16, 17, 21, 24, 25, 26, 33, 36, 37, 39, 41, 43]</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -4559,116 +4069,101 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>0.4884920634920634</t>
+          <t>0.47307692307692306</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>0.06072311778799257</t>
+          <t>0.06569276176529334</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>0.07168651988081066</t>
+          <t>0.0784053188945764</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>0.9238828650255555</t>
+          <t>0.9159681657709685</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>1.3229708671569824</t>
-        </is>
-      </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>3.206787586212158</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>[0, 2, 3, 12, 13, 15, 17, 18, 20, 21, 23, 25, 29, 33, 34, 37, 42, 43]</t>
+          <t>[0, 2, 5, 6, 8, 11, 12, 13, 14, 19, 23, 26, 27, 32, 33, 36, 38, 43, 44]</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>0.32996031746031745</t>
+          <t>0.5703296703296703</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>0.06615685691709268</t>
+          <t>0.06329808606101885</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>0.059528006578419876</t>
+          <t>0.0854895667736364</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>0.94751319738287</t>
+          <t>0.9000968861653486</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>1.3475399017333984</t>
-        </is>
-      </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>3.176863193511963</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>[3, 4, 7, 9, 11, 22, 23, 25, 26, 30, 33, 34, 35, 36, 39]</t>
+          <t>[0, 3, 4, 6, 8, 10, 12, 17, 19, 21, 22, 23, 25, 27, 29, 33, 35, 37, 42, 44]</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>0.34384920634920635</t>
+          <t>0.6543956043956044</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>0.06520404856962728</t>
+          <t>0.06491224586132374</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>0.06245355579915224</t>
+          <t>0.07569531102642789</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>0.9422274179209043</t>
+          <t>0.9216767413860208</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>1.3229730129241943</t>
-        </is>
-      </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>3.259148120880127</t>
         </is>
       </c>
     </row>
